--- a/JS/liste_personnel.xlsx
+++ b/JS/liste_personnel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1742F306-3A69-4F9B-A550-030E8F15619B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1A7B50-C338-482D-B37E-CBE3A2AED929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
+    <workbookView xWindow="4320" yWindow="1758" windowWidth="17280" windowHeight="10440" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1645,7 +1645,7 @@
     <col min="2" max="2" width="33.9453125" customWidth="1"/>
     <col min="3" max="3" width="34.26171875" customWidth="1"/>
     <col min="4" max="4" width="40.47265625" customWidth="1"/>
-    <col min="5" max="5" width="44.41796875" customWidth="1"/>
+    <col min="5" max="5" width="81.5234375" customWidth="1"/>
     <col min="6" max="6" width="38.578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1682,6 +1682,14 @@
       <c r="D2" s="7" t="s">
         <v>81</v>
       </c>
+      <c r="E2" t="str">
+        <f>"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/" &amp; A2 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/001.png</v>
+      </c>
+      <c r="F2" t="str">
+        <f>"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; A2 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/001.png</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
@@ -1696,6 +1704,14 @@
       <c r="D3" s="7" t="s">
         <v>83</v>
       </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E66" si="0">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/" &amp; A3 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/002.png</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F66" si="1">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; A3 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/002.png</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8" t="s">
@@ -1710,6 +1726,14 @@
       <c r="D4" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/003.png</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/003.png</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
@@ -1724,6 +1748,14 @@
       <c r="D5" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/004.png</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/004.png</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="8" t="s">
@@ -1738,6 +1770,14 @@
       <c r="D6" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/005.png</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/005.png</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="8" t="s">
@@ -1752,6 +1792,14 @@
       <c r="D7" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/006.png</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/006.png</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="8" t="s">
@@ -1766,6 +1814,14 @@
       <c r="D8" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/007.png</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/007.png</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9" t="s">
@@ -1780,6 +1836,14 @@
       <c r="D9" s="10" t="s">
         <v>94</v>
       </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/008.png</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/008.png</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="9" t="s">
@@ -1794,6 +1858,14 @@
       <c r="D10" s="5" t="s">
         <v>96</v>
       </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/009.png</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/009.png</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="9" t="s">
@@ -1808,6 +1880,14 @@
       <c r="D11" s="5" t="s">
         <v>98</v>
       </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/010.png</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/010.png</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9" t="s">
@@ -1822,6 +1902,14 @@
       <c r="D12" s="5" t="s">
         <v>100</v>
       </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/011.png</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/011.png</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9" t="s">
@@ -1836,6 +1924,14 @@
       <c r="D13" s="5" t="s">
         <v>100</v>
       </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/012.png</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/012.png</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8" t="s">
@@ -1850,6 +1946,14 @@
       <c r="D14" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/013.png</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/013.png</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8" t="s">
@@ -1864,6 +1968,14 @@
       <c r="D15" s="7" t="s">
         <v>105</v>
       </c>
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/014.png</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/014.png</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8" t="s">
@@ -1878,8 +1990,16 @@
       <c r="D16" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E16" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/015.png</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/015.png</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8" t="s">
         <v>108</v>
       </c>
@@ -1892,8 +2012,16 @@
       <c r="D17" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/016.png</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/016.png</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8" t="s">
         <v>110</v>
       </c>
@@ -1906,8 +2034,16 @@
       <c r="D18" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/017.png</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/017.png</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="8" t="s">
         <v>112</v>
       </c>
@@ -1920,8 +2056,16 @@
       <c r="D19" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/018.png</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/018.png</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="8" t="s">
         <v>114</v>
       </c>
@@ -1934,8 +2078,16 @@
       <c r="D20" s="7" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/019.png</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/019.png</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="8" t="s">
         <v>116</v>
       </c>
@@ -1948,8 +2100,16 @@
       <c r="D21" s="12" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/020.png</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/020.png</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="8" t="s">
         <v>118</v>
       </c>
@@ -1962,8 +2122,16 @@
       <c r="D22" s="7" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/021.png</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/021.png</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="8" t="s">
         <v>120</v>
       </c>
@@ -1976,8 +2144,16 @@
       <c r="D23" s="7" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/022.png</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/022.png</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8" t="s">
         <v>122</v>
       </c>
@@ -1990,8 +2166,16 @@
       <c r="D24" s="7" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/023.png</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/023.png</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8" t="s">
         <v>124</v>
       </c>
@@ -2004,8 +2188,16 @@
       <c r="D25" s="7" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/024.png</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/024.png</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8" t="s">
         <v>126</v>
       </c>
@@ -2018,8 +2210,16 @@
       <c r="D26" s="7" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/025.png</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/025.png</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="14" t="s">
         <v>128</v>
       </c>
@@ -2029,8 +2229,16 @@
       <c r="D27" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/026.png</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/026.png</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="14" t="s">
         <v>129</v>
       </c>
@@ -2043,8 +2251,16 @@
       <c r="D28" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/027.png</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/027.png</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="14" t="s">
         <v>130</v>
       </c>
@@ -2057,8 +2273,16 @@
       <c r="D29" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/028.png</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/028.png</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8" t="s">
         <v>132</v>
       </c>
@@ -2071,8 +2295,16 @@
       <c r="D30" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/029.png</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/029.png</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8" t="s">
         <v>134</v>
       </c>
@@ -2085,8 +2317,16 @@
       <c r="D31" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/030.png</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/030.png</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8" t="s">
         <v>136</v>
       </c>
@@ -2099,8 +2339,16 @@
       <c r="D32" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/031.png</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/031.png</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8" t="s">
         <v>138</v>
       </c>
@@ -2113,8 +2361,16 @@
       <c r="D33" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/032.png</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/032.png</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="8" t="s">
         <v>140</v>
       </c>
@@ -2127,8 +2383,16 @@
       <c r="D34" s="7" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/033.png</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/033.png</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="8" t="s">
         <v>142</v>
       </c>
@@ -2141,8 +2405,16 @@
       <c r="D35" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/034.png</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/034.png</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="8" t="s">
         <v>144</v>
       </c>
@@ -2155,8 +2427,16 @@
       <c r="D36" s="7" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/035.png</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/035.png</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8" t="s">
         <v>146</v>
       </c>
@@ -2169,8 +2449,16 @@
       <c r="D37" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E37" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/036.png</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/036.png</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
         <v>148</v>
       </c>
@@ -2183,8 +2471,16 @@
       <c r="D38" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E38" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/037.png</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/037.png</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="8" t="s">
         <v>150</v>
       </c>
@@ -2197,8 +2493,16 @@
       <c r="D39" s="7" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E39" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/038.png</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/038.png</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="8" t="s">
         <v>152</v>
       </c>
@@ -2211,8 +2515,16 @@
       <c r="D40" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E40" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/039.png</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/039.png</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="8" t="s">
         <v>154</v>
       </c>
@@ -2225,8 +2537,16 @@
       <c r="D41" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E41" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/040.png</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/040.png</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="8" t="s">
         <v>155</v>
       </c>
@@ -2239,8 +2559,16 @@
       <c r="D42" s="7" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E42" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/041.png</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/041.png</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="8" t="s">
         <v>157</v>
       </c>
@@ -2253,8 +2581,16 @@
       <c r="D43" s="7" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E43" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/042.png</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/042.png</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="8" t="s">
         <v>159</v>
       </c>
@@ -2267,8 +2603,16 @@
       <c r="D44" s="7" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E44" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/043.png</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/043.png</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="8" t="s">
         <v>161</v>
       </c>
@@ -2281,8 +2625,16 @@
       <c r="D45" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E45" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/044.png</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/044.png</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="8" t="s">
         <v>162</v>
       </c>
@@ -2295,8 +2647,16 @@
       <c r="D46" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E46" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/045.png</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/045.png</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="8" t="s">
         <v>164</v>
       </c>
@@ -2309,8 +2669,16 @@
       <c r="D47" s="7" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E47" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/046.png</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/046.png</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="8" t="s">
         <v>166</v>
       </c>
@@ -2323,8 +2691,16 @@
       <c r="D48" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E48" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/047.png</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/047.png</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="8" t="s">
         <v>168</v>
       </c>
@@ -2337,8 +2713,16 @@
       <c r="D49" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E49" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/048.png</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/048.png</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="8" t="s">
         <v>170</v>
       </c>
@@ -2351,8 +2735,16 @@
       <c r="D50" s="7" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E50" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/049.png</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/049.png</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="8" t="s">
         <v>172</v>
       </c>
@@ -2365,8 +2757,16 @@
       <c r="D51" s="7" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E51" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/050.png</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/050.png</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="16" t="s">
         <v>174</v>
       </c>
@@ -2379,8 +2779,16 @@
       <c r="D52" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E52" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/051.png</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/051.png</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="16" t="s">
         <v>176</v>
       </c>
@@ -2393,8 +2801,16 @@
       <c r="D53" s="7" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E53" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/052.png</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/052.png</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="8" t="s">
         <v>178</v>
       </c>
@@ -2407,8 +2823,16 @@
       <c r="D54" s="7" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E54" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/053.png</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/053.png</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="16" t="s">
         <v>180</v>
       </c>
@@ -2421,8 +2845,16 @@
       <c r="D55" s="7" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E55" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/054.png</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/054.png</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="16" t="s">
         <v>182</v>
       </c>
@@ -2435,8 +2867,16 @@
       <c r="D56" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E56" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/055.png</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/055.png</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="16" t="s">
         <v>184</v>
       </c>
@@ -2449,8 +2889,16 @@
       <c r="D57" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E57" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/056.png</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/056.png</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="16" t="s">
         <v>186</v>
       </c>
@@ -2463,8 +2911,16 @@
       <c r="D58" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E58" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/057.png</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/057.png</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="16" t="s">
         <v>188</v>
       </c>
@@ -2477,8 +2933,16 @@
       <c r="D59" s="7" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E59" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/058.png</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/058.png</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="8" t="s">
         <v>190</v>
       </c>
@@ -2491,8 +2955,16 @@
       <c r="D60" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E60" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/059.png</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/059.png</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="8" t="s">
         <v>192</v>
       </c>
@@ -2505,8 +2977,16 @@
       <c r="D61" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E61" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/060.png</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/060.png</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="8" t="s">
         <v>193</v>
       </c>
@@ -2519,8 +2999,16 @@
       <c r="D62" s="7" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E62" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/061.png</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/061.png</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="8" t="s">
         <v>195</v>
       </c>
@@ -2533,8 +3021,16 @@
       <c r="D63" s="7" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E63" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/062.png</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/062.png</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="8" t="s">
         <v>197</v>
       </c>
@@ -2547,8 +3043,16 @@
       <c r="D64" s="7" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E64" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/063.png</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/063.png</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="8" t="s">
         <v>199</v>
       </c>
@@ -2561,8 +3065,16 @@
       <c r="D65" s="4" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E65" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/064.png</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/064.png</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="8" t="s">
         <v>201</v>
       </c>
@@ -2575,8 +3087,16 @@
       <c r="D66" s="7" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E66" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/065.png</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/065.png</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="8" t="s">
         <v>203</v>
       </c>
@@ -2589,8 +3109,16 @@
       <c r="D67" s="7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E67" t="str">
+        <f t="shared" ref="E67:E96" si="2">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/" &amp; A67 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/066.png</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" ref="F67:F96" si="3">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; A67 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/066.png</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="8" t="s">
         <v>205</v>
       </c>
@@ -2603,8 +3131,16 @@
       <c r="D68" s="7" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E68" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/067.png</v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/067.png</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="8" t="s">
         <v>207</v>
       </c>
@@ -2617,8 +3153,16 @@
       <c r="D69" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E69" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/068.png</v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/068.png</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="8" t="s">
         <v>209</v>
       </c>
@@ -2631,8 +3175,16 @@
       <c r="D70" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E70" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/069.png</v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/069.png</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="8" t="s">
         <v>211</v>
       </c>
@@ -2645,8 +3197,16 @@
       <c r="D71" s="2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E71" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/070.png</v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/070.png</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="8" t="s">
         <v>213</v>
       </c>
@@ -2659,8 +3219,16 @@
       <c r="D72" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E72" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/071.png</v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/071.png</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="8" t="s">
         <v>215</v>
       </c>
@@ -2673,8 +3241,16 @@
       <c r="D73" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E73" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/072.png</v>
+      </c>
+      <c r="F73" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/072.png</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="8" t="s">
         <v>217</v>
       </c>
@@ -2687,8 +3263,16 @@
       <c r="D74" s="2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E74" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/073.png</v>
+      </c>
+      <c r="F74" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/073.png</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="8" t="s">
         <v>219</v>
       </c>
@@ -2701,8 +3285,16 @@
       <c r="D75" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E75" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/074.png</v>
+      </c>
+      <c r="F75" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/074.png</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="8" t="s">
         <v>221</v>
       </c>
@@ -2715,8 +3307,16 @@
       <c r="D76" s="7" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E76" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/075.png</v>
+      </c>
+      <c r="F76" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/075.png</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="8" t="s">
         <v>223</v>
       </c>
@@ -2729,8 +3329,16 @@
       <c r="D77" s="7" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E77" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/076.png</v>
+      </c>
+      <c r="F77" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/076.png</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="8" t="s">
         <v>225</v>
       </c>
@@ -2743,8 +3351,16 @@
       <c r="D78" s="7" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E78" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/077.png</v>
+      </c>
+      <c r="F78" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/077.png</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="8" t="s">
         <v>227</v>
       </c>
@@ -2757,8 +3373,16 @@
       <c r="D79" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E79" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/078.png</v>
+      </c>
+      <c r="F79" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/078.png</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="8" t="s">
         <v>228</v>
       </c>
@@ -2771,8 +3395,16 @@
       <c r="D80" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E80" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/079.png</v>
+      </c>
+      <c r="F80" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/079.png</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="8" t="s">
         <v>229</v>
       </c>
@@ -2785,8 +3417,16 @@
       <c r="D81" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E81" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/080.png</v>
+      </c>
+      <c r="F81" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/080.png</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="8" t="s">
         <v>230</v>
       </c>
@@ -2799,8 +3439,16 @@
       <c r="D82" s="2" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E82" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/081.png</v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/081.png</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="8" t="s">
         <v>232</v>
       </c>
@@ -2813,8 +3461,16 @@
       <c r="D83" s="3" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E83" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/082.png</v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/082.png</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="8" t="s">
         <v>234</v>
       </c>
@@ -2827,8 +3483,16 @@
       <c r="D84" s="2" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E84" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/083.png</v>
+      </c>
+      <c r="F84" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/083.png</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="18" t="s">
         <v>373</v>
       </c>
@@ -2841,8 +3505,16 @@
       <c r="D85" s="7" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E85" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/479 033.png</v>
+      </c>
+      <c r="F85" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/479 033.png</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="18" t="s">
         <v>372</v>
       </c>
@@ -2855,8 +3527,16 @@
       <c r="D86" s="4" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E86" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/377 286.png</v>
+      </c>
+      <c r="F86" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/377 286.png</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="18" t="s">
         <v>371</v>
       </c>
@@ -2869,8 +3549,16 @@
       <c r="D87" s="4" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E87" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/444 814.png</v>
+      </c>
+      <c r="F87" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/444 814.png</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="18"/>
       <c r="B88" s="6" t="s">
         <v>26</v>
@@ -2881,8 +3569,16 @@
       <c r="D88" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E88" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/.png</v>
+      </c>
+      <c r="F88" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/.png</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="18"/>
       <c r="B89" s="6" t="s">
         <v>48</v>
@@ -2893,8 +3589,16 @@
       <c r="D89" s="7" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E89" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/.png</v>
+      </c>
+      <c r="F89" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/.png</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="18" t="s">
         <v>367</v>
       </c>
@@ -2907,8 +3611,16 @@
       <c r="D90" s="2" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E90" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/478 287.png</v>
+      </c>
+      <c r="F90" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/478 287.png</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="18" t="s">
         <v>366</v>
       </c>
@@ -2921,8 +3633,16 @@
       <c r="D91" s="19" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E91" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/ .png</v>
+      </c>
+      <c r="F91" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/ .png</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="18" t="s">
         <v>374</v>
       </c>
@@ -2935,8 +3655,16 @@
       <c r="D92" s="19" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E92" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/406 731.png</v>
+      </c>
+      <c r="F92" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/406 731.png</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="18" t="s">
         <v>365</v>
       </c>
@@ -2949,8 +3677,16 @@
       <c r="D93" s="7" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E93" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/424 808.png</v>
+      </c>
+      <c r="F93" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/424 808.png</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="18" t="s">
         <v>368</v>
       </c>
@@ -2963,8 +3699,16 @@
       <c r="D94" s="5" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E94" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/453 178.png</v>
+      </c>
+      <c r="F94" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/453 178.png</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="18" t="s">
         <v>369</v>
       </c>
@@ -2977,8 +3721,16 @@
       <c r="D95" s="19" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E95" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/476 608.png</v>
+      </c>
+      <c r="F95" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/476 608.png</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="18" t="s">
         <v>370</v>
       </c>
@@ -2990,6 +3742,14 @@
       </c>
       <c r="D96" s="2" t="s">
         <v>246</v>
+      </c>
+      <c r="E96" t="str">
+        <f t="shared" si="2"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/458 510.png</v>
+      </c>
+      <c r="F96" t="str">
+        <f t="shared" si="3"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/458 510.png</v>
       </c>
     </row>
   </sheetData>

--- a/JS/liste_personnel.xlsx
+++ b/JS/liste_personnel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1A7B50-C338-482D-B37E-CBE3A2AED929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF42AED-42CE-4249-A59A-8A3C2DB78DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="1758" windowWidth="17280" windowHeight="10440" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
+    <workbookView xWindow="3984" yWindow="1422" windowWidth="17280" windowHeight="10440" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1687,8 +1687,8 @@
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/001.png</v>
       </c>
       <c r="F2" t="str">
-        <f>"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; A2 &amp; ".png"</f>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/001.png</v>
+        <f>"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/" &amp; A2 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/001.png</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1709,8 +1709,8 @@
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/002.png</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F66" si="1">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; A3 &amp; ".png"</f>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/002.png</v>
+        <f t="shared" ref="F3:F66" si="1">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/" &amp; A3 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/002.png</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F4" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/003.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/003.png</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="F5" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/004.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/004.png</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F6" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/005.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/005.png</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F7" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/006.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/006.png</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="F8" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/007.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/007.png</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="F9" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/008.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/008.png</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F10" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/009.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/009.png</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F11" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/010.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/010.png</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F12" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/011.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/011.png</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/012.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/012.png</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F14" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/013.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/013.png</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F15" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/014.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/014.png</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="F16" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/015.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/015.png</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="F17" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/016.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/016.png</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="F18" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/017.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/017.png</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F19" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/018.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/018.png</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F20" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/019.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/019.png</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F21" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/020.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/020.png</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F22" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/021.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/021.png</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F23" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/022.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/022.png</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F24" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/023.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/023.png</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F25" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/024.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/024.png</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F26" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/025.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/025.png</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F27" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/026.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/026.png</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F28" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/027.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/027.png</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="F29" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/028.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/028.png</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="F30" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/029.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/029.png</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F31" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/030.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/030.png</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="F32" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/031.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/031.png</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F33" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/032.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/032.png</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="F34" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/033.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/033.png</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="F35" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/034.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/034.png</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="F36" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/035.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/035.png</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="F37" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/036.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/036.png</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="F38" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/037.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/037.png</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="F39" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/038.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/038.png</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="F40" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/039.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/039.png</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F41" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/040.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/040.png</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F42" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/041.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/041.png</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F43" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/042.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/042.png</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F44" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/043.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/043.png</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="F45" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/044.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/044.png</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="F46" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/045.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/045.png</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F47" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/046.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/046.png</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="F48" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/047.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/047.png</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="F49" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/048.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/048.png</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F50" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/049.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/049.png</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="F51" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/050.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/050.png</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F52" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/051.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/051.png</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F53" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/052.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/052.png</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="F54" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/053.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/053.png</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F55" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/054.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/054.png</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="F56" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/055.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/055.png</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/056.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/056.png</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F58" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/057.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/057.png</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/058.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/058.png</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="F60" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/059.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/059.png</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F61" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/060.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/060.png</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F62" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/061.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/061.png</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F63" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/062.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/062.png</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="F64" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/063.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/063.png</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F65" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/064.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/064.png</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F66" t="str">
         <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/065.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/065.png</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3114,8 +3114,8 @@
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/066.png</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" ref="F67:F96" si="3">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; A67 &amp; ".png"</f>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/066.png</v>
+        <f t="shared" ref="F67:F96" si="3">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/" &amp; A67 &amp; ".png"</f>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/066.png</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F68" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/067.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/067.png</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F69" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/068.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/068.png</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F70" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/069.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/069.png</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="F71" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/070.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/070.png</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F72" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/071.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/071.png</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="F73" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/072.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/072.png</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="F74" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/073.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/073.png</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="F75" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/074.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/074.png</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="F76" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/075.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/075.png</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F77" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/076.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/076.png</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F78" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/077.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/077.png</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F79" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/078.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/078.png</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F80" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/079.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/079.png</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="F81" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/080.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/080.png</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="F82" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/081.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/081.png</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="F83" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/082.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/082.png</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F84" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/083.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/083.png</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="F85" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/479 033.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/479 033.png</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F86" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/377 286.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/377 286.png</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F87" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/444 814.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/444 814.png</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F88" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/.png</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="F89" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/.png</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3612,12 +3612,12 @@
         <v>240</v>
       </c>
       <c r="E90" t="str">
-        <f t="shared" si="2"/>
+        <f>"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/" &amp; A90 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/478 287.png</v>
       </c>
       <c r="F90" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/478 287.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/478 287.png</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="F91" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/ .png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/ .png</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="F92" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/406 731.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/406 731.png</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F93" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/424 808.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/424 808.png</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F94" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/453 178.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/453 178.png</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="F95" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/476 608.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/476 608.png</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F96" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/458 510.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/458 510.png</v>
       </c>
     </row>
   </sheetData>

--- a/JS/liste_personnel.xlsx
+++ b/JS/liste_personnel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF42AED-42CE-4249-A59A-8A3C2DB78DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD0F413-1F24-4EA5-B066-C3E062867711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3984" yWindow="1422" windowWidth="17280" windowHeight="10440" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="376">
   <si>
     <t>im</t>
   </si>
@@ -564,9 +564,6 @@
     <t>053</t>
   </si>
   <si>
-    <t>Secrétaire Responsable de la Communication auprès de l’Institut des Arts, des Lettres et Sciences Humaines (IALSH)</t>
-  </si>
-  <si>
     <t>054</t>
   </si>
   <si>
@@ -621,9 +618,6 @@
     <t>063</t>
   </si>
   <si>
-    <t>Responsable de suivi et archives auprès de la direction des Ressources Humaines</t>
-  </si>
-  <si>
     <t>064</t>
   </si>
   <si>
@@ -1122,34 +1116,43 @@
     <t>prenoms</t>
   </si>
   <si>
-    <t>424 808</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>478 287</t>
-  </si>
-  <si>
-    <t>453 178</t>
-  </si>
-  <si>
-    <t>476 608</t>
-  </si>
-  <si>
-    <t>458 510</t>
-  </si>
-  <si>
-    <t>444 814</t>
-  </si>
-  <si>
-    <t>377 286</t>
-  </si>
-  <si>
-    <t>479 033</t>
-  </si>
-  <si>
-    <t>406 731</t>
+    <t>479033</t>
+  </si>
+  <si>
+    <t>377286</t>
+  </si>
+  <si>
+    <t>444814</t>
+  </si>
+  <si>
+    <t>478287</t>
+  </si>
+  <si>
+    <t>406731</t>
+  </si>
+  <si>
+    <t>424808</t>
+  </si>
+  <si>
+    <t>453178</t>
+  </si>
+  <si>
+    <t>476608</t>
+  </si>
+  <si>
+    <t>458510</t>
+  </si>
+  <si>
+    <t>425002</t>
+  </si>
+  <si>
+    <t>Assistant Informatique auprès de l'Office du Baccalauréat</t>
+  </si>
+  <si>
+    <t>Responsable des gestions du personnel et des carrières auprès de la Direction des Ressources Humaines</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1677,7 +1680,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>81</v>
@@ -1762,10 +1765,10 @@
         <v>88</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>89</v>
@@ -1806,10 +1809,10 @@
         <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -1894,10 +1897,10 @@
         <v>99</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>100</v>
@@ -1941,7 +1944,7 @@
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>103</v>
@@ -2026,10 +2029,10 @@
         <v>110</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>111</v>
@@ -2070,10 +2073,10 @@
         <v>114</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>115</v>
@@ -2092,10 +2095,10 @@
         <v>116</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>117</v>
@@ -2117,7 +2120,7 @@
         <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>119</v>
@@ -2136,7 +2139,7 @@
         <v>120</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
         <v>60</v>
@@ -2205,7 +2208,7 @@
         <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>127</v>
@@ -2243,10 +2246,10 @@
         <v>129</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -2309,10 +2312,10 @@
         <v>134</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>135</v>
@@ -2375,10 +2378,10 @@
         <v>140</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>141</v>
@@ -2419,10 +2422,10 @@
         <v>144</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>145</v>
@@ -2441,10 +2444,10 @@
         <v>146</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>147</v>
@@ -2466,7 +2469,7 @@
         <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>149</v>
@@ -2488,7 +2491,7 @@
         <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>151</v>
@@ -2510,7 +2513,7 @@
         <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>153</v>
@@ -2573,10 +2576,10 @@
         <v>157</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C43" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>158</v>
@@ -2617,7 +2620,7 @@
         <v>161</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C45" t="s">
         <v>29</v>
@@ -2639,10 +2642,10 @@
         <v>162</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C46" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>163</v>
@@ -2661,10 +2664,10 @@
         <v>164</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C47" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>165</v>
@@ -2705,10 +2708,10 @@
         <v>168</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C49" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>169</v>
@@ -2749,10 +2752,10 @@
         <v>172</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>173</v>
@@ -2793,10 +2796,10 @@
         <v>176</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C53" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>177</v>
@@ -2810,18 +2813,18 @@
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/052.png</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="8" t="s">
         <v>178</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C54" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="0"/>
@@ -2834,16 +2837,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C55" t="s">
+        <v>292</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="C55" t="s">
-        <v>294</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="E55" t="str">
         <f t="shared" si="0"/>
@@ -2856,16 +2859,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E56" t="str">
         <f t="shared" si="0"/>
@@ -2878,16 +2881,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E57" t="str">
         <f t="shared" si="0"/>
@@ -2900,16 +2903,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C58" t="s">
+        <v>296</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C58" t="s">
-        <v>298</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="E58" t="str">
         <f t="shared" si="0"/>
@@ -2922,16 +2925,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C59" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E59" t="str">
         <f t="shared" si="0"/>
@@ -2944,16 +2947,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C60" t="s">
+        <v>299</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C60" t="s">
-        <v>301</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="E60" t="str">
         <f t="shared" si="0"/>
@@ -2966,13 +2969,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C61" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -2988,16 +2991,16 @@
     </row>
     <row r="62" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E62" t="str">
         <f t="shared" si="0"/>
@@ -3010,38 +3013,38 @@
     </row>
     <row r="63" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" t="s">
+        <v>303</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="E63" t="str">
+        <f t="shared" si="0"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/062.png</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="1"/>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/062.png</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>305</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E63" t="str">
-        <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/062.png</v>
-      </c>
-      <c r="F63" t="str">
-        <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/062.png</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C64" t="s">
-        <v>307</v>
-      </c>
       <c r="D64" s="7" t="s">
-        <v>198</v>
+        <v>375</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="0"/>
@@ -3054,16 +3057,16 @@
     </row>
     <row r="65" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C65" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E65" t="str">
         <f t="shared" si="0"/>
@@ -3076,16 +3079,16 @@
     </row>
     <row r="66" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C66" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E66" t="str">
         <f t="shared" si="0"/>
@@ -3098,16 +3101,16 @@
     </row>
     <row r="67" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C67" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E67" t="str">
         <f t="shared" ref="E67:E96" si="2">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/" &amp; A67 &amp; ".png"</f>
@@ -3120,16 +3123,16 @@
     </row>
     <row r="68" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C68" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E68" t="str">
         <f t="shared" si="2"/>
@@ -3142,16 +3145,16 @@
     </row>
     <row r="69" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C69" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E69" t="str">
         <f t="shared" si="2"/>
@@ -3164,16 +3167,16 @@
     </row>
     <row r="70" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C70" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E70" t="str">
         <f t="shared" si="2"/>
@@ -3186,16 +3189,16 @@
     </row>
     <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C71" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E71" t="str">
         <f t="shared" si="2"/>
@@ -3208,16 +3211,16 @@
     </row>
     <row r="72" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C72" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" si="2"/>
@@ -3230,16 +3233,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C73" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="2"/>
@@ -3252,16 +3255,16 @@
     </row>
     <row r="74" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C74" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="2"/>
@@ -3274,16 +3277,16 @@
     </row>
     <row r="75" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C75" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E75" t="str">
         <f t="shared" si="2"/>
@@ -3296,16 +3299,16 @@
     </row>
     <row r="76" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C76" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="2"/>
@@ -3318,16 +3321,16 @@
     </row>
     <row r="77" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C77" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E77" t="str">
         <f t="shared" si="2"/>
@@ -3340,16 +3343,16 @@
     </row>
     <row r="78" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C78" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E78" t="str">
         <f t="shared" si="2"/>
@@ -3362,16 +3365,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C79" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E79" t="str">
         <f t="shared" si="2"/>
@@ -3384,16 +3387,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C80" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E80" t="str">
         <f t="shared" si="2"/>
@@ -3406,16 +3409,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" si="2"/>
@@ -3428,16 +3431,16 @@
     </row>
     <row r="82" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C82" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E82" t="str">
         <f t="shared" si="2"/>
@@ -3450,16 +3453,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E83" t="str">
         <f t="shared" si="2"/>
@@ -3472,16 +3475,16 @@
     </row>
     <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C84" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E84" t="str">
         <f t="shared" si="2"/>
@@ -3494,68 +3497,68 @@
     </row>
     <row r="85" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="18" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C85" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/479 033.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/479033.png</v>
       </c>
       <c r="F85" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/479 033.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/479033.png</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="18" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C86" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/377 286.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/377286.png</v>
       </c>
       <c r="F86" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/377 286.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/377286.png</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="18" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C87" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/444 814.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/444814.png</v>
       </c>
       <c r="F87" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/444 814.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/444814.png</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3564,7 +3567,7 @@
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
@@ -3579,23 +3582,25 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="18"/>
+      <c r="A89" s="18" t="s">
+        <v>373</v>
+      </c>
       <c r="B89" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C89" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E89" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/425002.png</v>
       </c>
       <c r="F89" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/425002.png</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -3603,35 +3608,35 @@
         <v>367</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C90" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E90" t="str">
         <f>"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/" &amp; A90 &amp; ".png"</f>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/478 287.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/478287.png</v>
       </c>
       <c r="F90" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/478 287.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/478287.png</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="18" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C91" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E91" t="str">
         <f t="shared" si="2"/>
@@ -3644,51 +3649,51 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="18" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C92" t="s">
         <v>37</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E92" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/406 731.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/406731.png</v>
       </c>
       <c r="F92" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/406 731.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/406731.png</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C93" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E93" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/424 808.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/424808.png</v>
       </c>
       <c r="F93" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/424 808.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/424808.png</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>69</v>
@@ -3697,20 +3702,20 @@
         <v>70</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E94" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/453 178.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/453178.png</v>
       </c>
       <c r="F94" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/453 178.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/453178.png</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="18" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>19</v>
@@ -3719,37 +3724,37 @@
         <v>20</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E95" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/476 608.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/476608.png</v>
       </c>
       <c r="F95" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/476 608.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/476608.png</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="18" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C96" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="2"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/458 510.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/Photo_PAT/458510.png</v>
       </c>
       <c r="F96" t="str">
         <f t="shared" si="3"/>
-        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/458 510.png</v>
+        <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_personnel/458510.png</v>
       </c>
     </row>
   </sheetData>

--- a/JS/liste_personnel.xlsx
+++ b/JS/liste_personnel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD0F413-1F24-4EA5-B066-C3E062867711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7624F562-C61A-4EE9-81C6-A91C6614A268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3984" yWindow="1422" windowWidth="17280" windowHeight="10440" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{81980A95-F8B7-438D-9AA5-380F613A6664}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
